--- a/Day 6 Formatting data in an Excel Worksheet.xlsx
+++ b/Day 6 Formatting data in an Excel Worksheet.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Naik Balkrushna Anil\OneDrive\Attachments\Desktop\Full Stack Development\Exploring Data Science Field\Basic of Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F873CB23-D87B-440D-965B-3AD6B39F8320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFFBA316-0056-4F73-ABC4-5DE4E30326A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Formating Data in an Excel Shee" sheetId="1" r:id="rId1"/>
+    <sheet name="Conditional Formating" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="165">
   <si>
     <t>Trip_ID</t>
   </si>
@@ -193,36 +194,366 @@
   </si>
   <si>
     <t xml:space="preserve">Cell Styles and Custom </t>
+  </si>
+  <si>
+    <t>Student_100</t>
+  </si>
+  <si>
+    <t>Student_99</t>
+  </si>
+  <si>
+    <t>Student_98</t>
+  </si>
+  <si>
+    <t>Student_97</t>
+  </si>
+  <si>
+    <t>Student_96</t>
+  </si>
+  <si>
+    <t>Student_95</t>
+  </si>
+  <si>
+    <t>Student_94</t>
+  </si>
+  <si>
+    <t>Student_93</t>
+  </si>
+  <si>
+    <t>Student_92</t>
+  </si>
+  <si>
+    <t>Student_91</t>
+  </si>
+  <si>
+    <t>Student_90</t>
+  </si>
+  <si>
+    <t>Student_89</t>
+  </si>
+  <si>
+    <t>Student_88</t>
+  </si>
+  <si>
+    <t>Student_87</t>
+  </si>
+  <si>
+    <t>Student_86</t>
+  </si>
+  <si>
+    <t>Student_85</t>
+  </si>
+  <si>
+    <t>Student_84</t>
+  </si>
+  <si>
+    <t>Student_83</t>
+  </si>
+  <si>
+    <t>Student_82</t>
+  </si>
+  <si>
+    <t>Student_81</t>
+  </si>
+  <si>
+    <t>Student_80</t>
+  </si>
+  <si>
+    <t>Student_79</t>
+  </si>
+  <si>
+    <t>Student_78</t>
+  </si>
+  <si>
+    <t>Student_77</t>
+  </si>
+  <si>
+    <t>Student_76</t>
+  </si>
+  <si>
+    <t>Student_75</t>
+  </si>
+  <si>
+    <t>Student_74</t>
+  </si>
+  <si>
+    <t>Student_73</t>
+  </si>
+  <si>
+    <t>Student_72</t>
+  </si>
+  <si>
+    <t>Student_71</t>
+  </si>
+  <si>
+    <t>Student_70</t>
+  </si>
+  <si>
+    <t>Student_69</t>
+  </si>
+  <si>
+    <t>Student_68</t>
+  </si>
+  <si>
+    <t>Student_67</t>
+  </si>
+  <si>
+    <t>Student_66</t>
+  </si>
+  <si>
+    <t>Student_65</t>
+  </si>
+  <si>
+    <t>Student_64</t>
+  </si>
+  <si>
+    <t>Student_63</t>
+  </si>
+  <si>
+    <t>Student_62</t>
+  </si>
+  <si>
+    <t>Student_61</t>
+  </si>
+  <si>
+    <t>Student_60</t>
+  </si>
+  <si>
+    <t>Student_59</t>
+  </si>
+  <si>
+    <t>Student_58</t>
+  </si>
+  <si>
+    <t>Student_57</t>
+  </si>
+  <si>
+    <t>Student_56</t>
+  </si>
+  <si>
+    <t>Student_55</t>
+  </si>
+  <si>
+    <t>Student_54</t>
+  </si>
+  <si>
+    <t>Student_53</t>
+  </si>
+  <si>
+    <t>Student_52</t>
+  </si>
+  <si>
+    <t>Student_51</t>
+  </si>
+  <si>
+    <t>Student_50</t>
+  </si>
+  <si>
+    <t>Student_49</t>
+  </si>
+  <si>
+    <t>Student_48</t>
+  </si>
+  <si>
+    <t>Student_47</t>
+  </si>
+  <si>
+    <t>Student_46</t>
+  </si>
+  <si>
+    <t>Student_45</t>
+  </si>
+  <si>
+    <t>Student_44</t>
+  </si>
+  <si>
+    <t>Student_43</t>
+  </si>
+  <si>
+    <t>Student_42</t>
+  </si>
+  <si>
+    <t>Student_41</t>
+  </si>
+  <si>
+    <t>Student_40</t>
+  </si>
+  <si>
+    <t>Student_39</t>
+  </si>
+  <si>
+    <t>Student_38</t>
+  </si>
+  <si>
+    <t>Student_37</t>
+  </si>
+  <si>
+    <t>Student_36</t>
+  </si>
+  <si>
+    <t>Student_35</t>
+  </si>
+  <si>
+    <t>Student_34</t>
+  </si>
+  <si>
+    <t>Student_33</t>
+  </si>
+  <si>
+    <t>Student_32</t>
+  </si>
+  <si>
+    <t>Student_31</t>
+  </si>
+  <si>
+    <t>Student_30</t>
+  </si>
+  <si>
+    <t>Student_29</t>
+  </si>
+  <si>
+    <t>Student_28</t>
+  </si>
+  <si>
+    <t>Student_27</t>
+  </si>
+  <si>
+    <t>Student_26</t>
+  </si>
+  <si>
+    <t>Student_25</t>
+  </si>
+  <si>
+    <t>Student_24</t>
+  </si>
+  <si>
+    <t>Student_23</t>
+  </si>
+  <si>
+    <t>Student_22</t>
+  </si>
+  <si>
+    <t>Student_21</t>
+  </si>
+  <si>
+    <t>Student_20</t>
+  </si>
+  <si>
+    <t>Student_19</t>
+  </si>
+  <si>
+    <t>Student_18</t>
+  </si>
+  <si>
+    <t>Student_17</t>
+  </si>
+  <si>
+    <t>Student_16</t>
+  </si>
+  <si>
+    <t>Student_15</t>
+  </si>
+  <si>
+    <t>Student_14</t>
+  </si>
+  <si>
+    <t>Student_13</t>
+  </si>
+  <si>
+    <t>Student_12</t>
+  </si>
+  <si>
+    <t>Student_11</t>
+  </si>
+  <si>
+    <t>Student_10</t>
+  </si>
+  <si>
+    <t>Student_9</t>
+  </si>
+  <si>
+    <t>Student_8</t>
+  </si>
+  <si>
+    <t>Student_7</t>
+  </si>
+  <si>
+    <t>Student_6</t>
+  </si>
+  <si>
+    <t>Student_5</t>
+  </si>
+  <si>
+    <t>Student_4</t>
+  </si>
+  <si>
+    <t>Student_3</t>
+  </si>
+  <si>
+    <t>Student_2</t>
+  </si>
+  <si>
+    <t>Student_1</t>
+  </si>
+  <si>
+    <t>Student Name</t>
+  </si>
+  <si>
+    <t>Roll No</t>
+  </si>
+  <si>
+    <t>Math</t>
+  </si>
+  <si>
+    <t>Chem</t>
+  </si>
+  <si>
+    <t>Phy</t>
+  </si>
+  <si>
+    <t>Bio</t>
+  </si>
+  <si>
+    <t>Social Sci</t>
+  </si>
+  <si>
+    <t>Percentage</t>
+  </si>
+  <si>
+    <t>Result</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Gill Sans MT"/>
+      <name val="Trebuchet MS"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Gill Sans MT"/>
+      <name val="Trebuchet MS"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Gill Sans MT"/>
+      <name val="Trebuchet MS"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -255,6 +586,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,10 +708,10 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -400,13 +743,121 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="2" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -431,7 +882,7 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>579249</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>45796</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -469,9 +920,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Dividend">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Facet">
   <a:themeElements>
-    <a:clrScheme name="Dividend">
+    <a:clrScheme name="Facet">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -479,48 +930,46 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="3D3D3D"/>
+        <a:srgbClr val="2C3C43"/>
       </a:dk2>
       <a:lt2>
         <a:srgbClr val="EBEBEB"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4D1434"/>
+        <a:srgbClr val="90C226"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="903163"/>
+        <a:srgbClr val="54A021"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="B2324B"/>
+        <a:srgbClr val="E6B91E"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="969FA7"/>
+        <a:srgbClr val="E76618"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="66B1CE"/>
+        <a:srgbClr val="C42F1A"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="40619D"/>
+        <a:srgbClr val="918655"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="828282"/>
+        <a:srgbClr val="99CA3C"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="B9D181"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Dividend">
+    <a:fontScheme name="Facet">
       <a:majorFont>
-        <a:latin typeface="Gill Sans MT" panose="020B0502020104020203"/>
+        <a:latin typeface="Trebuchet MS" panose="020B0603020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Grek" typeface="Corbel"/>
-        <a:font script="Cyrl" typeface="Corbel"/>
-        <a:font script="Jpan" typeface="HGｺﾞｼｯｸE"/>
-        <a:font script="Hang" typeface="휴먼매직체"/>
-        <a:font script="Hans" typeface="华文中宋"/>
+        <a:font script="Jpan" typeface="メイリオ"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="方正姚体"/>
         <a:font script="Hant" typeface="微軟正黑體"/>
-        <a:font script="Arab" typeface="Majalla UI"/>
+        <a:font script="Arab" typeface="Tahoma"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
@@ -548,18 +997,16 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Gill Sans MT" panose="020B0502020104020203"/>
+        <a:latin typeface="Trebuchet MS" panose="020B0603020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Grek" typeface="Corbel"/>
-        <a:font script="Cyrl" typeface="Corbel"/>
-        <a:font script="Jpan" typeface="HGｺﾞｼｯｸE"/>
-        <a:font script="Hang" typeface="휴먼매직체"/>
-        <a:font script="Hans" typeface="华文中宋"/>
+        <a:font script="Jpan" typeface="メイリオ"/>
+        <a:font script="Hang" typeface="HY그래픽M"/>
+        <a:font script="Hans" typeface="华文新魏"/>
         <a:font script="Hant" typeface="微軟正黑體"/>
-        <a:font script="Arab" typeface="Majalla UI"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
+        <a:font script="Arab" typeface="Tahoma"/>
+        <a:font script="Hebr" typeface="Gisha"/>
+        <a:font script="Thai" typeface="IrisUPC"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -580,12 +1027,12 @@
         <a:font script="Laoo" typeface="DokChampa"/>
         <a:font script="Sinh" typeface="Iskoola Pota"/>
         <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Tahoma"/>
+        <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Dividend">
+    <a:fmtScheme name="Facet">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -594,32 +1041,30 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="68000"/>
-                <a:alpha val="90000"/>
-                <a:lumMod val="100000"/>
+                <a:tint val="65000"/>
+                <a:lumMod val="110000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="100000">
+            <a:gs pos="88000">
               <a:schemeClr val="phClr">
                 <a:tint val="90000"/>
-                <a:lumMod val="95000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:lumMod val="110000"/>
+                <a:tint val="96000"/>
+                <a:lumMod val="100000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="84000">
+            <a:gs pos="78000">
               <a:schemeClr val="phClr">
-                <a:shade val="90000"/>
-                <a:lumMod val="88000"/>
+                <a:shade val="94000"/>
+                <a:lumMod val="94000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -629,13 +1074,11 @@
       <a:lnStyleLst>
         <a:ln w="12700" cap="rnd" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:lumMod val="90000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="22225" cap="rnd" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cap="rnd" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -656,16 +1099,16 @@
           <a:effectLst>
             <a:outerShdw blurRad="38100" dist="25400" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="55000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="88900" dist="38100" dir="5040000" rotWithShape="0">
+            <a:outerShdw blurRad="50800" dist="38100" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="60000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -673,12 +1116,10 @@
             <a:camera prst="orthographicFront">
               <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="tl">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
+            <a:lightRig rig="threePt" dir="tl"/>
           </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="38100" h="50800"/>
+          <a:sp3d prstMaterial="plastic">
+            <a:bevelT w="0" h="0"/>
           </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
@@ -691,14 +1132,13 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="90000"/>
-                <a:lumMod val="110000"/>
+                <a:lumMod val="104000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="88000">
+            <a:gs pos="94000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="110000"/>
-                <a:lumMod val="88000"/>
+                <a:shade val="96000"/>
+                <a:lumMod val="82000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -714,9 +1154,8 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="98000"/>
-                <a:satMod val="110000"/>
-                <a:lumMod val="86000"/>
+                <a:shade val="94000"/>
+                <a:lumMod val="96000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -731,7 +1170,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Dividend" id="{9697A71B-4AB7-4A1A-BD5B-BB2D22835B57}" vid="{C21699FF-00E4-43C8-BBCC-D7E5536C3717}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Facet" id="{C0C680CD-088A-49FC-A102-D699147F32B2}" vid="{CFBC31BA-B70F-4F30-BCAA-4F3011E16C4D}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -740,13 +1179,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L21"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="10" width="15.77734375" customWidth="1"/>
     <col min="12" max="12" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -778,7 +1217,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1001</v>
       </c>
@@ -808,7 +1247,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>1002</v>
       </c>
@@ -840,7 +1279,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>1003</v>
       </c>
@@ -872,7 +1311,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>1004</v>
       </c>
@@ -904,7 +1343,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>1005</v>
       </c>
@@ -936,7 +1375,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>1006</v>
       </c>
@@ -968,7 +1407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>1007</v>
       </c>
@@ -1000,7 +1439,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>1008</v>
       </c>
@@ -1035,7 +1474,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>1009</v>
       </c>
@@ -1067,7 +1506,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7">
         <v>1010</v>
       </c>
@@ -1099,18 +1538,18 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="6:9" x14ac:dyDescent="0.5">
+    <row r="17" spans="6:9" x14ac:dyDescent="0.3">
       <c r="I17" s="11" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="6:9" x14ac:dyDescent="0.5">
+    <row r="19" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F19" s="1" t="s">
         <v>52</v>
       </c>
       <c r="G19" s="1"/>
     </row>
-    <row r="21" spans="6:9" x14ac:dyDescent="0.5">
+    <row r="21" spans="6:9" x14ac:dyDescent="0.3">
       <c r="F21" t="s">
         <v>53</v>
       </c>
@@ -1119,4 +1558,3163 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94913A8A-2F5A-4852-8F9F-CF40B6C2D630}">
+  <dimension ref="A1:I101"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="7" width="14.33203125" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="14">
+        <v>1</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="14">
+        <v>77</v>
+      </c>
+      <c r="D2" s="14">
+        <v>44</v>
+      </c>
+      <c r="E2" s="14">
+        <v>75</v>
+      </c>
+      <c r="F2" s="14">
+        <v>84</v>
+      </c>
+      <c r="G2" s="14">
+        <v>46</v>
+      </c>
+      <c r="H2" s="16">
+        <f>SUM(C2:G2)/500</f>
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="I2" t="str">
+        <f>IF(H2&gt;0.6, "Pass", "Fail")</f>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="14">
+        <v>2</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="14">
+        <v>44</v>
+      </c>
+      <c r="D3" s="14">
+        <v>84</v>
+      </c>
+      <c r="E3" s="14">
+        <v>98</v>
+      </c>
+      <c r="F3" s="14">
+        <v>76</v>
+      </c>
+      <c r="G3" s="14">
+        <v>68</v>
+      </c>
+      <c r="H3" s="16">
+        <f t="shared" ref="H3:H66" si="0">SUM(C3:G3)/500</f>
+        <v>0.74</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I66" si="1">IF(H3&gt;0.6, "Pass", "Fail")</f>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="14">
+        <v>3</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="14">
+        <v>42</v>
+      </c>
+      <c r="D4" s="14">
+        <v>40</v>
+      </c>
+      <c r="E4" s="14">
+        <v>79</v>
+      </c>
+      <c r="F4" s="14">
+        <v>55</v>
+      </c>
+      <c r="G4" s="14">
+        <v>63</v>
+      </c>
+      <c r="H4" s="16">
+        <f t="shared" si="0"/>
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="14">
+        <v>4</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C5" s="14">
+        <v>54</v>
+      </c>
+      <c r="D5" s="14">
+        <v>73</v>
+      </c>
+      <c r="E5" s="14">
+        <v>47</v>
+      </c>
+      <c r="F5" s="14">
+        <v>85</v>
+      </c>
+      <c r="G5" s="14">
+        <v>59</v>
+      </c>
+      <c r="H5" s="16">
+        <f t="shared" si="0"/>
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="14">
+        <v>5</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="14">
+        <v>74</v>
+      </c>
+      <c r="D6" s="14">
+        <v>47</v>
+      </c>
+      <c r="E6" s="14">
+        <v>82</v>
+      </c>
+      <c r="F6" s="14">
+        <v>91</v>
+      </c>
+      <c r="G6" s="14">
+        <v>55</v>
+      </c>
+      <c r="H6" s="16">
+        <f t="shared" si="0"/>
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="14">
+        <v>6</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" s="14">
+        <v>62</v>
+      </c>
+      <c r="D7" s="14">
+        <v>78</v>
+      </c>
+      <c r="E7" s="14">
+        <v>40</v>
+      </c>
+      <c r="F7" s="14">
+        <v>60</v>
+      </c>
+      <c r="G7" s="14">
+        <v>60</v>
+      </c>
+      <c r="H7" s="16">
+        <f t="shared" si="0"/>
+        <v>0.6</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="14">
+        <v>7</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="C8" s="14">
+        <v>79</v>
+      </c>
+      <c r="D8" s="14">
+        <v>59</v>
+      </c>
+      <c r="E8" s="14">
+        <v>60</v>
+      </c>
+      <c r="F8" s="14">
+        <v>36</v>
+      </c>
+      <c r="G8" s="14">
+        <v>99</v>
+      </c>
+      <c r="H8" s="16">
+        <f t="shared" si="0"/>
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="14">
+        <v>8</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="14">
+        <v>80</v>
+      </c>
+      <c r="D9" s="14">
+        <v>73</v>
+      </c>
+      <c r="E9" s="14">
+        <v>67</v>
+      </c>
+      <c r="F9" s="14">
+        <v>99</v>
+      </c>
+      <c r="G9" s="14">
+        <v>65</v>
+      </c>
+      <c r="H9" s="16">
+        <f t="shared" si="0"/>
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A10" s="14">
+        <v>9</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" s="14">
+        <v>59</v>
+      </c>
+      <c r="D10" s="14">
+        <v>95</v>
+      </c>
+      <c r="E10" s="14">
+        <v>43</v>
+      </c>
+      <c r="F10" s="14">
+        <v>74</v>
+      </c>
+      <c r="G10" s="14">
+        <v>51</v>
+      </c>
+      <c r="H10" s="16">
+        <f t="shared" si="0"/>
+        <v>0.64400000000000002</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="14">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="C11" s="14">
+        <v>92</v>
+      </c>
+      <c r="D11" s="14">
+        <v>52</v>
+      </c>
+      <c r="E11" s="14">
+        <v>65</v>
+      </c>
+      <c r="F11" s="14">
+        <v>43</v>
+      </c>
+      <c r="G11" s="14">
+        <v>78</v>
+      </c>
+      <c r="H11" s="16">
+        <f t="shared" si="0"/>
+        <v>0.66</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="14">
+        <v>11</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="C12" s="14">
+        <v>63</v>
+      </c>
+      <c r="D12" s="14">
+        <v>78</v>
+      </c>
+      <c r="E12" s="14">
+        <v>90</v>
+      </c>
+      <c r="F12" s="14">
+        <v>78</v>
+      </c>
+      <c r="G12" s="14">
+        <v>38</v>
+      </c>
+      <c r="H12" s="16">
+        <f t="shared" si="0"/>
+        <v>0.69399999999999995</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="14">
+        <v>12</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="C13" s="14">
+        <v>54</v>
+      </c>
+      <c r="D13" s="14">
+        <v>88</v>
+      </c>
+      <c r="E13" s="14">
+        <v>78</v>
+      </c>
+      <c r="F13" s="14">
+        <v>47</v>
+      </c>
+      <c r="G13" s="14">
+        <v>53</v>
+      </c>
+      <c r="H13" s="16">
+        <f t="shared" si="0"/>
+        <v>0.64</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="14">
+        <v>37</v>
+      </c>
+      <c r="D14" s="14">
+        <v>35</v>
+      </c>
+      <c r="E14" s="14">
+        <v>89</v>
+      </c>
+      <c r="F14" s="14">
+        <v>67</v>
+      </c>
+      <c r="G14" s="14">
+        <v>89</v>
+      </c>
+      <c r="H14" s="16">
+        <f t="shared" si="0"/>
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="14">
+        <v>14</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="14">
+        <v>51</v>
+      </c>
+      <c r="D15" s="14">
+        <v>53</v>
+      </c>
+      <c r="E15" s="14">
+        <v>87</v>
+      </c>
+      <c r="F15" s="14">
+        <v>66</v>
+      </c>
+      <c r="G15" s="14">
+        <v>48</v>
+      </c>
+      <c r="H15" s="16">
+        <f t="shared" si="0"/>
+        <v>0.61</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="14">
+        <v>15</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="C16" s="14">
+        <v>91</v>
+      </c>
+      <c r="D16" s="14">
+        <v>52</v>
+      </c>
+      <c r="E16" s="14">
+        <v>78</v>
+      </c>
+      <c r="F16" s="14">
+        <v>80</v>
+      </c>
+      <c r="G16" s="14">
+        <v>88</v>
+      </c>
+      <c r="H16" s="16">
+        <f t="shared" si="0"/>
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="14">
+        <v>16</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="14">
+        <v>40</v>
+      </c>
+      <c r="D17" s="14">
+        <v>63</v>
+      </c>
+      <c r="E17" s="14">
+        <v>83</v>
+      </c>
+      <c r="F17" s="14">
+        <v>66</v>
+      </c>
+      <c r="G17" s="14">
+        <v>72</v>
+      </c>
+      <c r="H17" s="16">
+        <f t="shared" si="0"/>
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="I17" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="14">
+        <v>17</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="14">
+        <v>65</v>
+      </c>
+      <c r="D18" s="14">
+        <v>46</v>
+      </c>
+      <c r="E18" s="14">
+        <v>61</v>
+      </c>
+      <c r="F18" s="14">
+        <v>75</v>
+      </c>
+      <c r="G18" s="14">
+        <v>57</v>
+      </c>
+      <c r="H18" s="16">
+        <f t="shared" si="0"/>
+        <v>0.60799999999999998</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="14">
+        <v>18</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" s="14">
+        <v>66</v>
+      </c>
+      <c r="D19" s="14">
+        <v>61</v>
+      </c>
+      <c r="E19" s="14">
+        <v>87</v>
+      </c>
+      <c r="F19" s="14">
+        <v>79</v>
+      </c>
+      <c r="G19" s="14">
+        <v>57</v>
+      </c>
+      <c r="H19" s="16">
+        <f t="shared" si="0"/>
+        <v>0.7</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A20" s="14">
+        <v>19</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C20" s="14">
+        <v>50</v>
+      </c>
+      <c r="D20" s="14">
+        <v>59</v>
+      </c>
+      <c r="E20" s="14">
+        <v>55</v>
+      </c>
+      <c r="F20" s="14">
+        <v>85</v>
+      </c>
+      <c r="G20" s="14">
+        <v>66</v>
+      </c>
+      <c r="H20" s="16">
+        <f t="shared" si="0"/>
+        <v>0.63</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="14">
+        <v>20</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" s="14">
+        <v>47</v>
+      </c>
+      <c r="D21" s="14">
+        <v>47</v>
+      </c>
+      <c r="E21" s="14">
+        <v>39</v>
+      </c>
+      <c r="F21" s="14">
+        <v>61</v>
+      </c>
+      <c r="G21" s="14">
+        <v>99</v>
+      </c>
+      <c r="H21" s="16">
+        <f t="shared" si="0"/>
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="I21" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="14">
+        <v>21</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C22" s="14">
+        <v>83</v>
+      </c>
+      <c r="D22" s="14">
+        <v>89</v>
+      </c>
+      <c r="E22" s="14">
+        <v>83</v>
+      </c>
+      <c r="F22" s="14">
+        <v>60</v>
+      </c>
+      <c r="G22" s="14">
+        <v>41</v>
+      </c>
+      <c r="H22" s="16">
+        <f t="shared" si="0"/>
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="I22" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="14">
+        <v>22</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="C23" s="14">
+        <v>55</v>
+      </c>
+      <c r="D23" s="14">
+        <v>60</v>
+      </c>
+      <c r="E23" s="14">
+        <v>73</v>
+      </c>
+      <c r="F23" s="14">
+        <v>51</v>
+      </c>
+      <c r="G23" s="14">
+        <v>45</v>
+      </c>
+      <c r="H23" s="16">
+        <f t="shared" si="0"/>
+        <v>0.56799999999999995</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="14">
+        <v>23</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="C24" s="14">
+        <v>73</v>
+      </c>
+      <c r="D24" s="14">
+        <v>53</v>
+      </c>
+      <c r="E24" s="14">
+        <v>38</v>
+      </c>
+      <c r="F24" s="14">
+        <v>81</v>
+      </c>
+      <c r="G24" s="14">
+        <v>88</v>
+      </c>
+      <c r="H24" s="16">
+        <f t="shared" si="0"/>
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="I24" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A25" s="14">
+        <v>24</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="14">
+        <v>44</v>
+      </c>
+      <c r="D25" s="14">
+        <v>78</v>
+      </c>
+      <c r="E25" s="14">
+        <v>76</v>
+      </c>
+      <c r="F25" s="14">
+        <v>90</v>
+      </c>
+      <c r="G25" s="14">
+        <v>84</v>
+      </c>
+      <c r="H25" s="16">
+        <f t="shared" si="0"/>
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="14">
+        <v>25</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="14">
+        <v>70</v>
+      </c>
+      <c r="D26" s="14">
+        <v>85</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>46</v>
+      </c>
+      <c r="G26" s="14">
+        <v>93</v>
+      </c>
+      <c r="H26" s="16">
+        <f t="shared" si="0"/>
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="14">
+        <v>26</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="14">
+        <v>69</v>
+      </c>
+      <c r="D27" s="14">
+        <v>46</v>
+      </c>
+      <c r="E27" s="14">
+        <v>64</v>
+      </c>
+      <c r="F27" s="14">
+        <v>55</v>
+      </c>
+      <c r="G27" s="14">
+        <v>41</v>
+      </c>
+      <c r="H27" s="16">
+        <f t="shared" si="0"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="14">
+        <v>27</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="C28" s="14">
+        <v>86</v>
+      </c>
+      <c r="D28" s="14">
+        <v>66</v>
+      </c>
+      <c r="E28" s="14">
+        <v>45</v>
+      </c>
+      <c r="F28" s="14">
+        <v>41</v>
+      </c>
+      <c r="G28" s="14">
+        <v>36</v>
+      </c>
+      <c r="H28" s="16">
+        <f t="shared" si="0"/>
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="14">
+        <v>28</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="C29" s="14">
+        <v>47</v>
+      </c>
+      <c r="D29" s="14">
+        <v>91</v>
+      </c>
+      <c r="E29" s="14">
+        <v>99</v>
+      </c>
+      <c r="F29" s="14">
+        <v>49</v>
+      </c>
+      <c r="G29" s="14">
+        <v>46</v>
+      </c>
+      <c r="H29" s="16">
+        <f t="shared" si="0"/>
+        <v>0.66400000000000003</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="14">
+        <v>29</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="C30" s="14">
+        <v>79</v>
+      </c>
+      <c r="D30" s="14">
+        <v>100</v>
+      </c>
+      <c r="E30" s="14">
+        <v>78</v>
+      </c>
+      <c r="F30" s="14">
+        <v>95</v>
+      </c>
+      <c r="G30" s="14">
+        <v>69</v>
+      </c>
+      <c r="H30" s="16">
+        <f t="shared" si="0"/>
+        <v>0.84199999999999997</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A31" s="14">
+        <v>30</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="14">
+        <v>41</v>
+      </c>
+      <c r="D31" s="14">
+        <v>54</v>
+      </c>
+      <c r="E31" s="14">
+        <v>80</v>
+      </c>
+      <c r="F31" s="14">
+        <v>81</v>
+      </c>
+      <c r="G31" s="14">
+        <v>81</v>
+      </c>
+      <c r="H31" s="16">
+        <f t="shared" si="0"/>
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="14">
+        <v>31</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="14">
+        <v>79</v>
+      </c>
+      <c r="D32" s="14">
+        <v>89</v>
+      </c>
+      <c r="E32" s="14">
+        <v>81</v>
+      </c>
+      <c r="F32" s="14">
+        <v>39</v>
+      </c>
+      <c r="G32" s="14">
+        <v>90</v>
+      </c>
+      <c r="H32" s="16">
+        <f t="shared" si="0"/>
+        <v>0.75600000000000001</v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A33" s="14">
+        <v>32</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C33" s="14">
+        <v>88</v>
+      </c>
+      <c r="D33" s="14">
+        <v>56</v>
+      </c>
+      <c r="E33" s="14">
+        <v>86</v>
+      </c>
+      <c r="F33" s="14">
+        <v>60</v>
+      </c>
+      <c r="G33" s="14">
+        <v>85</v>
+      </c>
+      <c r="H33" s="16">
+        <f t="shared" si="0"/>
+        <v>0.75</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="14">
+        <v>33</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C34" s="14">
+        <v>90</v>
+      </c>
+      <c r="D34" s="14">
+        <v>44</v>
+      </c>
+      <c r="E34" s="14">
+        <v>36</v>
+      </c>
+      <c r="F34" s="14">
+        <v>87</v>
+      </c>
+      <c r="G34" s="14">
+        <v>37</v>
+      </c>
+      <c r="H34" s="16">
+        <f t="shared" si="0"/>
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A35" s="14">
+        <v>34</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="14">
+        <v>58</v>
+      </c>
+      <c r="D35" s="14">
+        <v>43</v>
+      </c>
+      <c r="E35" s="14">
+        <v>64</v>
+      </c>
+      <c r="F35" s="14">
+        <v>77</v>
+      </c>
+      <c r="G35" s="14">
+        <v>53</v>
+      </c>
+      <c r="H35" s="16">
+        <f t="shared" si="0"/>
+        <v>0.59</v>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A36" s="14">
+        <v>35</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C36" s="14">
+        <v>76</v>
+      </c>
+      <c r="D36" s="14">
+        <v>82</v>
+      </c>
+      <c r="E36" s="14">
+        <v>72</v>
+      </c>
+      <c r="F36" s="14">
+        <v>93</v>
+      </c>
+      <c r="G36" s="14">
+        <v>98</v>
+      </c>
+      <c r="H36" s="16">
+        <f t="shared" si="0"/>
+        <v>0.84199999999999997</v>
+      </c>
+      <c r="I36" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A37" s="14">
+        <v>36</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" s="14">
+        <v>47</v>
+      </c>
+      <c r="D37" s="14">
+        <v>80</v>
+      </c>
+      <c r="E37" s="14">
+        <v>51</v>
+      </c>
+      <c r="F37" s="14">
+        <v>51</v>
+      </c>
+      <c r="G37" s="14">
+        <v>60</v>
+      </c>
+      <c r="H37" s="16">
+        <f t="shared" si="0"/>
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="I37" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A38" s="14">
+        <v>37</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="14">
+        <v>91</v>
+      </c>
+      <c r="D38" s="14">
+        <v>35</v>
+      </c>
+      <c r="E38" s="14">
+        <v>44</v>
+      </c>
+      <c r="F38" s="14">
+        <v>66</v>
+      </c>
+      <c r="G38" s="14">
+        <v>62</v>
+      </c>
+      <c r="H38" s="16">
+        <f t="shared" si="0"/>
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="I38" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A39" s="14">
+        <v>38</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C39" s="14">
+        <v>80</v>
+      </c>
+      <c r="D39" s="14">
+        <v>63</v>
+      </c>
+      <c r="E39" s="14">
+        <v>93</v>
+      </c>
+      <c r="F39" s="14">
+        <v>95</v>
+      </c>
+      <c r="G39" s="14">
+        <v>91</v>
+      </c>
+      <c r="H39" s="16">
+        <f t="shared" si="0"/>
+        <v>0.84399999999999997</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A40" s="14">
+        <v>39</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="14">
+        <v>51</v>
+      </c>
+      <c r="D40" s="14">
+        <v>57</v>
+      </c>
+      <c r="E40" s="14">
+        <v>48</v>
+      </c>
+      <c r="F40" s="14">
+        <v>83</v>
+      </c>
+      <c r="G40" s="14">
+        <v>50</v>
+      </c>
+      <c r="H40" s="16">
+        <f t="shared" si="0"/>
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="14">
+        <v>40</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41" s="14">
+        <v>95</v>
+      </c>
+      <c r="D41" s="14">
+        <v>56</v>
+      </c>
+      <c r="E41" s="14">
+        <v>42</v>
+      </c>
+      <c r="F41" s="14">
+        <v>84</v>
+      </c>
+      <c r="G41" s="14">
+        <v>82</v>
+      </c>
+      <c r="H41" s="16">
+        <f t="shared" si="0"/>
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="14">
+        <v>41</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42" s="14">
+        <v>75</v>
+      </c>
+      <c r="D42" s="14">
+        <v>99</v>
+      </c>
+      <c r="E42" s="14">
+        <v>58</v>
+      </c>
+      <c r="F42" s="14">
+        <v>47</v>
+      </c>
+      <c r="G42" s="14">
+        <v>42</v>
+      </c>
+      <c r="H42" s="16">
+        <f t="shared" si="0"/>
+        <v>0.64200000000000002</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="14">
+        <v>42</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="C43" s="14">
+        <v>97</v>
+      </c>
+      <c r="D43" s="14">
+        <v>44</v>
+      </c>
+      <c r="E43" s="14">
+        <v>59</v>
+      </c>
+      <c r="F43" s="14">
+        <v>79</v>
+      </c>
+      <c r="G43" s="14">
+        <v>60</v>
+      </c>
+      <c r="H43" s="16">
+        <f t="shared" si="0"/>
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="14">
+        <v>43</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" s="14">
+        <v>96</v>
+      </c>
+      <c r="D44" s="14">
+        <v>91</v>
+      </c>
+      <c r="E44" s="14">
+        <v>78</v>
+      </c>
+      <c r="F44" s="14">
+        <v>49</v>
+      </c>
+      <c r="G44" s="14">
+        <v>86</v>
+      </c>
+      <c r="H44" s="16">
+        <f t="shared" si="0"/>
+        <v>0.8</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A45" s="14">
+        <v>44</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45" s="14">
+        <v>82</v>
+      </c>
+      <c r="D45" s="14">
+        <v>86</v>
+      </c>
+      <c r="E45" s="14">
+        <v>68</v>
+      </c>
+      <c r="F45" s="14">
+        <v>93</v>
+      </c>
+      <c r="G45" s="14">
+        <v>85</v>
+      </c>
+      <c r="H45" s="16">
+        <f t="shared" si="0"/>
+        <v>0.82799999999999996</v>
+      </c>
+      <c r="I45" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A46" s="14">
+        <v>45</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" s="14">
+        <v>72</v>
+      </c>
+      <c r="D46" s="14">
+        <v>56</v>
+      </c>
+      <c r="E46" s="14">
+        <v>82</v>
+      </c>
+      <c r="F46" s="14">
+        <v>93</v>
+      </c>
+      <c r="G46" s="14">
+        <v>79</v>
+      </c>
+      <c r="H46" s="16">
+        <f t="shared" si="0"/>
+        <v>0.76400000000000001</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A47" s="14">
+        <v>46</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C47" s="14">
+        <v>87</v>
+      </c>
+      <c r="D47" s="14">
+        <v>79</v>
+      </c>
+      <c r="E47" s="14">
+        <v>52</v>
+      </c>
+      <c r="F47" s="14">
+        <v>79</v>
+      </c>
+      <c r="G47" s="14">
+        <v>86</v>
+      </c>
+      <c r="H47" s="16">
+        <f t="shared" si="0"/>
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A48" s="14">
+        <v>47</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" s="14">
+        <v>73</v>
+      </c>
+      <c r="D48" s="14">
+        <v>44</v>
+      </c>
+      <c r="E48" s="14">
+        <v>89</v>
+      </c>
+      <c r="F48" s="14">
+        <v>87</v>
+      </c>
+      <c r="G48" s="14">
+        <v>46</v>
+      </c>
+      <c r="H48" s="16">
+        <f t="shared" si="0"/>
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="I48" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A49" s="14">
+        <v>48</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" s="14">
+        <v>40</v>
+      </c>
+      <c r="D49" s="14">
+        <v>94</v>
+      </c>
+      <c r="E49" s="14">
+        <v>82</v>
+      </c>
+      <c r="F49" s="14">
+        <v>43</v>
+      </c>
+      <c r="G49" s="14">
+        <v>93</v>
+      </c>
+      <c r="H49" s="16">
+        <f t="shared" si="0"/>
+        <v>0.70399999999999996</v>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A50" s="14">
+        <v>49</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="C50" s="14">
+        <v>68</v>
+      </c>
+      <c r="D50" s="14">
+        <v>61</v>
+      </c>
+      <c r="E50" s="14">
+        <v>70</v>
+      </c>
+      <c r="F50" s="14">
+        <v>45</v>
+      </c>
+      <c r="G50" s="14">
+        <v>55</v>
+      </c>
+      <c r="H50" s="16">
+        <f t="shared" si="0"/>
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="I50" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A51" s="14">
+        <v>50</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C51" s="14">
+        <v>73</v>
+      </c>
+      <c r="D51" s="14">
+        <v>81</v>
+      </c>
+      <c r="E51" s="14">
+        <v>79</v>
+      </c>
+      <c r="F51" s="14">
+        <v>85</v>
+      </c>
+      <c r="G51" s="14">
+        <v>83</v>
+      </c>
+      <c r="H51" s="16">
+        <f t="shared" si="0"/>
+        <v>0.80200000000000005</v>
+      </c>
+      <c r="I51" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A52" s="14">
+        <v>51</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C52" s="14">
+        <v>72</v>
+      </c>
+      <c r="D52" s="14">
+        <v>79</v>
+      </c>
+      <c r="E52" s="14">
+        <v>100</v>
+      </c>
+      <c r="F52" s="14">
+        <v>76</v>
+      </c>
+      <c r="G52" s="14">
+        <v>56</v>
+      </c>
+      <c r="H52" s="16">
+        <f t="shared" si="0"/>
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="I52" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="14">
+        <v>52</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" s="14">
+        <v>87</v>
+      </c>
+      <c r="D53" s="14">
+        <v>83</v>
+      </c>
+      <c r="E53" s="14">
+        <v>51</v>
+      </c>
+      <c r="F53" s="14">
+        <v>60</v>
+      </c>
+      <c r="G53" s="14">
+        <v>49</v>
+      </c>
+      <c r="H53" s="16">
+        <f t="shared" si="0"/>
+        <v>0.66</v>
+      </c>
+      <c r="I53" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A54" s="14">
+        <v>53</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="14">
+        <v>88</v>
+      </c>
+      <c r="D54" s="14">
+        <v>91</v>
+      </c>
+      <c r="E54" s="14">
+        <v>85</v>
+      </c>
+      <c r="F54" s="14">
+        <v>46</v>
+      </c>
+      <c r="G54" s="14">
+        <v>61</v>
+      </c>
+      <c r="H54" s="16">
+        <f t="shared" si="0"/>
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="I54" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A55" s="14">
+        <v>54</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="C55" s="14">
+        <v>71</v>
+      </c>
+      <c r="D55" s="14">
+        <v>97</v>
+      </c>
+      <c r="E55" s="14">
+        <v>94</v>
+      </c>
+      <c r="F55" s="14">
+        <v>49</v>
+      </c>
+      <c r="G55" s="14">
+        <v>68</v>
+      </c>
+      <c r="H55" s="16">
+        <f t="shared" si="0"/>
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="I55" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A56" s="14">
+        <v>55</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="C56" s="14">
+        <v>49</v>
+      </c>
+      <c r="D56" s="14">
+        <v>62</v>
+      </c>
+      <c r="E56" s="14">
+        <v>55</v>
+      </c>
+      <c r="F56" s="14">
+        <v>47</v>
+      </c>
+      <c r="G56" s="14">
+        <v>97</v>
+      </c>
+      <c r="H56" s="16">
+        <f t="shared" si="0"/>
+        <v>0.62</v>
+      </c>
+      <c r="I56" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A57" s="14">
+        <v>56</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C57" s="14">
+        <v>88</v>
+      </c>
+      <c r="D57" s="14">
+        <v>84</v>
+      </c>
+      <c r="E57" s="14">
+        <v>39</v>
+      </c>
+      <c r="F57" s="14">
+        <v>75</v>
+      </c>
+      <c r="G57" s="14">
+        <v>69</v>
+      </c>
+      <c r="H57" s="16">
+        <f t="shared" si="0"/>
+        <v>0.71</v>
+      </c>
+      <c r="I57" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A58" s="14">
+        <v>57</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="C58" s="14">
+        <v>68</v>
+      </c>
+      <c r="D58" s="14">
+        <v>37</v>
+      </c>
+      <c r="E58" s="14">
+        <v>63</v>
+      </c>
+      <c r="F58" s="14">
+        <v>42</v>
+      </c>
+      <c r="G58" s="14">
+        <v>40</v>
+      </c>
+      <c r="H58" s="16">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="I58" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A59" s="14">
+        <v>58</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C59" s="14">
+        <v>42</v>
+      </c>
+      <c r="D59" s="14">
+        <v>97</v>
+      </c>
+      <c r="E59" s="14">
+        <v>42</v>
+      </c>
+      <c r="F59" s="14">
+        <v>37</v>
+      </c>
+      <c r="G59" s="14">
+        <v>75</v>
+      </c>
+      <c r="H59" s="16">
+        <f t="shared" si="0"/>
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="I59" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A60" s="14">
+        <v>59</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C60" s="14">
+        <v>72</v>
+      </c>
+      <c r="D60" s="14">
+        <v>66</v>
+      </c>
+      <c r="E60" s="14">
+        <v>40</v>
+      </c>
+      <c r="F60" s="14">
+        <v>79</v>
+      </c>
+      <c r="G60" s="14">
+        <v>68</v>
+      </c>
+      <c r="H60" s="16">
+        <f t="shared" si="0"/>
+        <v>0.65</v>
+      </c>
+      <c r="I60" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="14">
+        <v>60</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C61" s="14">
+        <v>72</v>
+      </c>
+      <c r="D61" s="14">
+        <v>45</v>
+      </c>
+      <c r="E61" s="14">
+        <v>40</v>
+      </c>
+      <c r="F61" s="14">
+        <v>63</v>
+      </c>
+      <c r="G61" s="14">
+        <v>86</v>
+      </c>
+      <c r="H61" s="16">
+        <f t="shared" si="0"/>
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="I61" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="14">
+        <v>61</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>95</v>
+      </c>
+      <c r="C62" s="14">
+        <v>79</v>
+      </c>
+      <c r="D62" s="14">
+        <v>91</v>
+      </c>
+      <c r="E62" s="14">
+        <v>73</v>
+      </c>
+      <c r="F62" s="14">
+        <v>51</v>
+      </c>
+      <c r="G62" s="14">
+        <v>54</v>
+      </c>
+      <c r="H62" s="16">
+        <f t="shared" si="0"/>
+        <v>0.69599999999999995</v>
+      </c>
+      <c r="I62" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A63" s="14">
+        <v>62</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C63" s="14">
+        <v>43</v>
+      </c>
+      <c r="D63" s="14">
+        <v>41</v>
+      </c>
+      <c r="E63" s="14">
+        <v>92</v>
+      </c>
+      <c r="F63" s="14">
+        <v>64</v>
+      </c>
+      <c r="G63" s="14">
+        <v>54</v>
+      </c>
+      <c r="H63" s="16">
+        <f t="shared" si="0"/>
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="I63" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="14">
+        <v>63</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="14">
+        <v>85</v>
+      </c>
+      <c r="D64" s="14">
+        <v>46</v>
+      </c>
+      <c r="E64" s="14">
+        <v>83</v>
+      </c>
+      <c r="F64" s="14">
+        <v>41</v>
+      </c>
+      <c r="G64" s="14">
+        <v>97</v>
+      </c>
+      <c r="H64" s="16">
+        <f t="shared" si="0"/>
+        <v>0.70399999999999996</v>
+      </c>
+      <c r="I64" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A65" s="14">
+        <v>64</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C65" s="14">
+        <v>51</v>
+      </c>
+      <c r="D65" s="14">
+        <v>100</v>
+      </c>
+      <c r="E65" s="14">
+        <v>98</v>
+      </c>
+      <c r="F65" s="14">
+        <v>39</v>
+      </c>
+      <c r="G65" s="14">
+        <v>41</v>
+      </c>
+      <c r="H65" s="16">
+        <f t="shared" si="0"/>
+        <v>0.65800000000000003</v>
+      </c>
+      <c r="I65" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A66" s="14">
+        <v>65</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C66" s="14">
+        <v>92</v>
+      </c>
+      <c r="D66" s="14">
+        <v>79</v>
+      </c>
+      <c r="E66" s="14">
+        <v>54</v>
+      </c>
+      <c r="F66" s="14">
+        <v>74</v>
+      </c>
+      <c r="G66" s="14">
+        <v>86</v>
+      </c>
+      <c r="H66" s="16">
+        <f t="shared" si="0"/>
+        <v>0.77</v>
+      </c>
+      <c r="I66" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A67" s="14">
+        <v>66</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C67" s="14">
+        <v>56</v>
+      </c>
+      <c r="D67" s="14">
+        <v>94</v>
+      </c>
+      <c r="E67" s="14">
+        <v>60</v>
+      </c>
+      <c r="F67" s="14">
+        <v>89</v>
+      </c>
+      <c r="G67" s="14">
+        <v>56</v>
+      </c>
+      <c r="H67" s="16">
+        <f t="shared" ref="H67:H101" si="2">SUM(C67:G67)/500</f>
+        <v>0.71</v>
+      </c>
+      <c r="I67" t="str">
+        <f t="shared" ref="I67:I101" si="3">IF(H67&gt;0.6, "Pass", "Fail")</f>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A68" s="14">
+        <v>67</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="C68" s="14">
+        <v>66</v>
+      </c>
+      <c r="D68" s="14">
+        <v>49</v>
+      </c>
+      <c r="E68" s="14">
+        <v>39</v>
+      </c>
+      <c r="F68" s="14">
+        <v>37</v>
+      </c>
+      <c r="G68" s="14">
+        <v>47</v>
+      </c>
+      <c r="H68" s="16">
+        <f t="shared" si="2"/>
+        <v>0.47599999999999998</v>
+      </c>
+      <c r="I68" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A69" s="14">
+        <v>68</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" s="14">
+        <v>42</v>
+      </c>
+      <c r="D69" s="14">
+        <v>69</v>
+      </c>
+      <c r="E69" s="14">
+        <v>71</v>
+      </c>
+      <c r="F69" s="14">
+        <v>39</v>
+      </c>
+      <c r="G69" s="14">
+        <v>40</v>
+      </c>
+      <c r="H69" s="16">
+        <f t="shared" si="2"/>
+        <v>0.52200000000000002</v>
+      </c>
+      <c r="I69" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A70" s="14">
+        <v>69</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C70" s="14">
+        <v>48</v>
+      </c>
+      <c r="D70" s="14">
+        <v>48</v>
+      </c>
+      <c r="E70" s="14">
+        <v>91</v>
+      </c>
+      <c r="F70" s="14">
+        <v>40</v>
+      </c>
+      <c r="G70" s="14">
+        <v>50</v>
+      </c>
+      <c r="H70" s="16">
+        <f t="shared" si="2"/>
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="I70" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A71" s="14">
+        <v>70</v>
+      </c>
+      <c r="B71" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C71" s="14">
+        <v>42</v>
+      </c>
+      <c r="D71" s="14">
+        <v>77</v>
+      </c>
+      <c r="E71" s="14">
+        <v>48</v>
+      </c>
+      <c r="F71" s="14">
+        <v>47</v>
+      </c>
+      <c r="G71" s="14">
+        <v>99</v>
+      </c>
+      <c r="H71" s="16">
+        <f t="shared" si="2"/>
+        <v>0.626</v>
+      </c>
+      <c r="I71" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A72" s="14">
+        <v>71</v>
+      </c>
+      <c r="B72" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C72" s="14">
+        <v>68</v>
+      </c>
+      <c r="D72" s="14">
+        <v>40</v>
+      </c>
+      <c r="E72" s="14">
+        <v>50</v>
+      </c>
+      <c r="F72" s="14">
+        <v>66</v>
+      </c>
+      <c r="G72" s="14">
+        <v>84</v>
+      </c>
+      <c r="H72" s="16">
+        <f t="shared" si="2"/>
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="I72" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A73" s="14">
+        <v>72</v>
+      </c>
+      <c r="B73" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="C73" s="14">
+        <v>43</v>
+      </c>
+      <c r="D73" s="14">
+        <v>66</v>
+      </c>
+      <c r="E73" s="14">
+        <v>97</v>
+      </c>
+      <c r="F73" s="14">
+        <v>43</v>
+      </c>
+      <c r="G73" s="14">
+        <v>68</v>
+      </c>
+      <c r="H73" s="16">
+        <f t="shared" si="2"/>
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="I73" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A74" s="14">
+        <v>73</v>
+      </c>
+      <c r="B74" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" s="14">
+        <v>35</v>
+      </c>
+      <c r="D74" s="14">
+        <v>82</v>
+      </c>
+      <c r="E74" s="14">
+        <v>80</v>
+      </c>
+      <c r="F74" s="14">
+        <v>44</v>
+      </c>
+      <c r="G74" s="14">
+        <v>53</v>
+      </c>
+      <c r="H74" s="16">
+        <f t="shared" si="2"/>
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="I74" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A75" s="14">
+        <v>74</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C75" s="14">
+        <v>77</v>
+      </c>
+      <c r="D75" s="14">
+        <v>45</v>
+      </c>
+      <c r="E75" s="14">
+        <v>97</v>
+      </c>
+      <c r="F75" s="14">
+        <v>54</v>
+      </c>
+      <c r="G75" s="14">
+        <v>86</v>
+      </c>
+      <c r="H75" s="16">
+        <f t="shared" si="2"/>
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="I75" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A76" s="14">
+        <v>75</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C76" s="14">
+        <v>35</v>
+      </c>
+      <c r="D76" s="14">
+        <v>89</v>
+      </c>
+      <c r="E76" s="14">
+        <v>44</v>
+      </c>
+      <c r="F76" s="14">
+        <v>39</v>
+      </c>
+      <c r="G76" s="14">
+        <v>84</v>
+      </c>
+      <c r="H76" s="16">
+        <f t="shared" si="2"/>
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="I76" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A77" s="14">
+        <v>76</v>
+      </c>
+      <c r="B77" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="C77" s="14">
+        <v>92</v>
+      </c>
+      <c r="D77" s="14">
+        <v>52</v>
+      </c>
+      <c r="E77" s="14">
+        <v>78</v>
+      </c>
+      <c r="F77" s="14">
+        <v>48</v>
+      </c>
+      <c r="G77" s="14">
+        <v>76</v>
+      </c>
+      <c r="H77" s="16">
+        <f t="shared" si="2"/>
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="I77" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A78" s="14">
+        <v>77</v>
+      </c>
+      <c r="B78" s="14" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" s="14">
+        <v>95</v>
+      </c>
+      <c r="D78" s="14">
+        <v>59</v>
+      </c>
+      <c r="E78" s="14">
+        <v>41</v>
+      </c>
+      <c r="F78" s="14">
+        <v>54</v>
+      </c>
+      <c r="G78" s="14">
+        <v>97</v>
+      </c>
+      <c r="H78" s="16">
+        <f t="shared" si="2"/>
+        <v>0.69199999999999995</v>
+      </c>
+      <c r="I78" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A79" s="14">
+        <v>78</v>
+      </c>
+      <c r="B79" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C79" s="14">
+        <v>65</v>
+      </c>
+      <c r="D79" s="14">
+        <v>49</v>
+      </c>
+      <c r="E79" s="14">
+        <v>72</v>
+      </c>
+      <c r="F79" s="14">
+        <v>68</v>
+      </c>
+      <c r="G79" s="14">
+        <v>100</v>
+      </c>
+      <c r="H79" s="16">
+        <f t="shared" si="2"/>
+        <v>0.70799999999999996</v>
+      </c>
+      <c r="I79" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A80" s="14">
+        <v>79</v>
+      </c>
+      <c r="B80" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="C80" s="14">
+        <v>60</v>
+      </c>
+      <c r="D80" s="14">
+        <v>87</v>
+      </c>
+      <c r="E80" s="14">
+        <v>49</v>
+      </c>
+      <c r="F80" s="14">
+        <v>56</v>
+      </c>
+      <c r="G80" s="14">
+        <v>58</v>
+      </c>
+      <c r="H80" s="16">
+        <f t="shared" si="2"/>
+        <v>0.62</v>
+      </c>
+      <c r="I80" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A81" s="14">
+        <v>80</v>
+      </c>
+      <c r="B81" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C81" s="14">
+        <v>36</v>
+      </c>
+      <c r="D81" s="14">
+        <v>40</v>
+      </c>
+      <c r="E81" s="14">
+        <v>57</v>
+      </c>
+      <c r="F81" s="14">
+        <v>100</v>
+      </c>
+      <c r="G81" s="14">
+        <v>76</v>
+      </c>
+      <c r="H81" s="16">
+        <f t="shared" si="2"/>
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="I81" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A82" s="14">
+        <v>81</v>
+      </c>
+      <c r="B82" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C82" s="14">
+        <v>56</v>
+      </c>
+      <c r="D82" s="14">
+        <v>80</v>
+      </c>
+      <c r="E82" s="14">
+        <v>96</v>
+      </c>
+      <c r="F82" s="14">
+        <v>85</v>
+      </c>
+      <c r="G82" s="14">
+        <v>95</v>
+      </c>
+      <c r="H82" s="16">
+        <f t="shared" si="2"/>
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="I82" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A83" s="14">
+        <v>82</v>
+      </c>
+      <c r="B83" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C83" s="14">
+        <v>75</v>
+      </c>
+      <c r="D83" s="14">
+        <v>54</v>
+      </c>
+      <c r="E83" s="14">
+        <v>42</v>
+      </c>
+      <c r="F83" s="14">
+        <v>63</v>
+      </c>
+      <c r="G83" s="14">
+        <v>100</v>
+      </c>
+      <c r="H83" s="16">
+        <f t="shared" si="2"/>
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="I83" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A84" s="14">
+        <v>83</v>
+      </c>
+      <c r="B84" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C84" s="14">
+        <v>99</v>
+      </c>
+      <c r="D84" s="14">
+        <v>100</v>
+      </c>
+      <c r="E84" s="14">
+        <v>78</v>
+      </c>
+      <c r="F84" s="14">
+        <v>83</v>
+      </c>
+      <c r="G84" s="14">
+        <v>92</v>
+      </c>
+      <c r="H84" s="16">
+        <f t="shared" si="2"/>
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="I84" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A85" s="14">
+        <v>84</v>
+      </c>
+      <c r="B85" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C85" s="14">
+        <v>41</v>
+      </c>
+      <c r="D85" s="14">
+        <v>54</v>
+      </c>
+      <c r="E85" s="14">
+        <v>63</v>
+      </c>
+      <c r="F85" s="14">
+        <v>50</v>
+      </c>
+      <c r="G85" s="14">
+        <v>71</v>
+      </c>
+      <c r="H85" s="16">
+        <f t="shared" si="2"/>
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="I85" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A86" s="14">
+        <v>85</v>
+      </c>
+      <c r="B86" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="C86" s="14">
+        <v>38</v>
+      </c>
+      <c r="D86" s="14">
+        <v>53</v>
+      </c>
+      <c r="E86" s="14">
+        <v>60</v>
+      </c>
+      <c r="F86" s="14">
+        <v>46</v>
+      </c>
+      <c r="G86" s="14">
+        <v>52</v>
+      </c>
+      <c r="H86" s="16">
+        <f t="shared" si="2"/>
+        <v>0.498</v>
+      </c>
+      <c r="I86" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A87" s="14">
+        <v>86</v>
+      </c>
+      <c r="B87" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C87" s="14">
+        <v>69</v>
+      </c>
+      <c r="D87" s="14">
+        <v>54</v>
+      </c>
+      <c r="E87" s="14">
+        <v>58</v>
+      </c>
+      <c r="F87" s="14">
+        <v>94</v>
+      </c>
+      <c r="G87" s="14">
+        <v>80</v>
+      </c>
+      <c r="H87" s="16">
+        <f t="shared" si="2"/>
+        <v>0.71</v>
+      </c>
+      <c r="I87" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A88" s="14">
+        <v>87</v>
+      </c>
+      <c r="B88" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="C88" s="14">
+        <v>74</v>
+      </c>
+      <c r="D88" s="14">
+        <v>60</v>
+      </c>
+      <c r="E88" s="14">
+        <v>81</v>
+      </c>
+      <c r="F88" s="14">
+        <v>87</v>
+      </c>
+      <c r="G88" s="14">
+        <v>41</v>
+      </c>
+      <c r="H88" s="16">
+        <f t="shared" si="2"/>
+        <v>0.68600000000000005</v>
+      </c>
+      <c r="I88" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A89" s="14">
+        <v>88</v>
+      </c>
+      <c r="B89" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C89" s="14">
+        <v>95</v>
+      </c>
+      <c r="D89" s="14">
+        <v>100</v>
+      </c>
+      <c r="E89" s="14">
+        <v>56</v>
+      </c>
+      <c r="F89" s="14">
+        <v>97</v>
+      </c>
+      <c r="G89" s="14">
+        <v>39</v>
+      </c>
+      <c r="H89" s="16">
+        <f t="shared" si="2"/>
+        <v>0.77400000000000002</v>
+      </c>
+      <c r="I89" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A90" s="14">
+        <v>89</v>
+      </c>
+      <c r="B90" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C90" s="14">
+        <v>46</v>
+      </c>
+      <c r="D90" s="14">
+        <v>54</v>
+      </c>
+      <c r="E90" s="14">
+        <v>66</v>
+      </c>
+      <c r="F90" s="14">
+        <v>36</v>
+      </c>
+      <c r="G90" s="14">
+        <v>87</v>
+      </c>
+      <c r="H90" s="16">
+        <f t="shared" si="2"/>
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="I90" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A91" s="14">
+        <v>90</v>
+      </c>
+      <c r="B91" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="C91" s="14">
+        <v>66</v>
+      </c>
+      <c r="D91" s="14">
+        <v>87</v>
+      </c>
+      <c r="E91" s="14">
+        <v>74</v>
+      </c>
+      <c r="F91" s="14">
+        <v>66</v>
+      </c>
+      <c r="G91" s="14">
+        <v>45</v>
+      </c>
+      <c r="H91" s="16">
+        <f t="shared" si="2"/>
+        <v>0.67600000000000005</v>
+      </c>
+      <c r="I91" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A92" s="14">
+        <v>91</v>
+      </c>
+      <c r="B92" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C92" s="14">
+        <v>46</v>
+      </c>
+      <c r="D92" s="14">
+        <v>57</v>
+      </c>
+      <c r="E92" s="14">
+        <v>62</v>
+      </c>
+      <c r="F92" s="14">
+        <v>77</v>
+      </c>
+      <c r="G92" s="14">
+        <v>85</v>
+      </c>
+      <c r="H92" s="16">
+        <f t="shared" si="2"/>
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="I92" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A93" s="14">
+        <v>92</v>
+      </c>
+      <c r="B93" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C93" s="14">
+        <v>90</v>
+      </c>
+      <c r="D93" s="14">
+        <v>71</v>
+      </c>
+      <c r="E93" s="14">
+        <v>56</v>
+      </c>
+      <c r="F93" s="14">
+        <v>79</v>
+      </c>
+      <c r="G93" s="14">
+        <v>41</v>
+      </c>
+      <c r="H93" s="16">
+        <f t="shared" si="2"/>
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="I93" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A94" s="14">
+        <v>93</v>
+      </c>
+      <c r="B94" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="C94" s="14">
+        <v>83</v>
+      </c>
+      <c r="D94" s="14">
+        <v>78</v>
+      </c>
+      <c r="E94" s="14">
+        <v>72</v>
+      </c>
+      <c r="F94" s="14">
+        <v>66</v>
+      </c>
+      <c r="G94" s="14">
+        <v>74</v>
+      </c>
+      <c r="H94" s="16">
+        <f t="shared" si="2"/>
+        <v>0.746</v>
+      </c>
+      <c r="I94" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A95" s="14">
+        <v>94</v>
+      </c>
+      <c r="B95" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C95" s="14">
+        <v>68</v>
+      </c>
+      <c r="D95" s="14">
+        <v>71</v>
+      </c>
+      <c r="E95" s="14">
+        <v>57</v>
+      </c>
+      <c r="F95" s="14">
+        <v>71</v>
+      </c>
+      <c r="G95" s="14">
+        <v>59</v>
+      </c>
+      <c r="H95" s="16">
+        <f t="shared" si="2"/>
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="I95" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A96" s="14">
+        <v>95</v>
+      </c>
+      <c r="B96" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C96" s="14">
+        <v>52</v>
+      </c>
+      <c r="D96" s="14">
+        <v>54</v>
+      </c>
+      <c r="E96" s="14">
+        <v>50</v>
+      </c>
+      <c r="F96" s="14">
+        <v>35</v>
+      </c>
+      <c r="G96" s="14">
+        <v>43</v>
+      </c>
+      <c r="H96" s="16">
+        <f t="shared" si="2"/>
+        <v>0.46800000000000003</v>
+      </c>
+      <c r="I96" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A97" s="14">
+        <v>96</v>
+      </c>
+      <c r="B97" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C97" s="14">
+        <v>83</v>
+      </c>
+      <c r="D97" s="14">
+        <v>46</v>
+      </c>
+      <c r="E97" s="14">
+        <v>36</v>
+      </c>
+      <c r="F97" s="14">
+        <v>89</v>
+      </c>
+      <c r="G97" s="14">
+        <v>45</v>
+      </c>
+      <c r="H97" s="16">
+        <f t="shared" si="2"/>
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="I97" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A98" s="14">
+        <v>97</v>
+      </c>
+      <c r="B98" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="C98" s="14">
+        <v>91</v>
+      </c>
+      <c r="D98" s="14">
+        <v>55</v>
+      </c>
+      <c r="E98" s="14">
+        <v>49</v>
+      </c>
+      <c r="F98" s="14">
+        <v>54</v>
+      </c>
+      <c r="G98" s="14">
+        <v>67</v>
+      </c>
+      <c r="H98" s="16">
+        <f t="shared" si="2"/>
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="I98" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A99" s="14">
+        <v>98</v>
+      </c>
+      <c r="B99" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C99" s="14">
+        <v>94</v>
+      </c>
+      <c r="D99" s="14">
+        <v>65</v>
+      </c>
+      <c r="E99" s="14">
+        <v>83</v>
+      </c>
+      <c r="F99" s="14">
+        <v>79</v>
+      </c>
+      <c r="G99" s="14">
+        <v>71</v>
+      </c>
+      <c r="H99" s="16">
+        <f t="shared" si="2"/>
+        <v>0.78400000000000003</v>
+      </c>
+      <c r="I99" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A100" s="14">
+        <v>99</v>
+      </c>
+      <c r="B100" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C100" s="14">
+        <v>100</v>
+      </c>
+      <c r="D100" s="14">
+        <v>45</v>
+      </c>
+      <c r="E100" s="14">
+        <v>77</v>
+      </c>
+      <c r="F100" s="14">
+        <v>84</v>
+      </c>
+      <c r="G100" s="14">
+        <v>63</v>
+      </c>
+      <c r="H100" s="16">
+        <f t="shared" si="2"/>
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="I100" t="str">
+        <f t="shared" si="3"/>
+        <v>Pass</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A101" s="14">
+        <v>100</v>
+      </c>
+      <c r="B101" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C101" s="14">
+        <v>65</v>
+      </c>
+      <c r="D101" s="14">
+        <v>68</v>
+      </c>
+      <c r="E101" s="14">
+        <v>46</v>
+      </c>
+      <c r="F101" s="14">
+        <v>60</v>
+      </c>
+      <c r="G101" s="14">
+        <v>59</v>
+      </c>
+      <c r="H101" s="16">
+        <f t="shared" si="2"/>
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="I101" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C1:G101 H1:I1">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+      <formula>90</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I101">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Pass">
+      <formula>NOT(ISERROR(SEARCH("Pass",I2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Fail">
+      <formula>NOT(ISERROR(SEARCH("Fail",I2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>